--- a/data/demo/Юго-восток бригады.xlsx
+++ b/data/demo/Юго-восток бригады.xlsx
@@ -464,7 +464,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Весёлая, д. 33 к 6</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,7 +488,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>55.430185, 37.780207</t>
+          <t>Домодедово, ул.25 лет Октября, д. 5</t>
         </is>
       </c>
     </row>
@@ -506,7 +510,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.842111, 38.237871</t>
+          <t>Кашира, ул.Южная, д. 5</t>
         </is>
       </c>
     </row>
@@ -528,7 +532,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.832756, 38.229883</t>
+          <t>Кашира, ул.Центральная, д. 8</t>
         </is>
       </c>
     </row>
@@ -548,7 +552,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Город Москва, б-р.Ореховый, д. 24 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -566,7 +574,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Шипиловская, д. 22</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -584,7 +596,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Город Москва, ш.Каширское, д. 92 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -602,7 +618,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Ягодная, д. 6</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -620,7 +640,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Город Москва, проезд.Луговой, д. 12 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,7 +662,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Бехтерева, д. 15с2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,7 +686,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.410537, 37.837823</t>
+          <t>Домодедово, ул.Ильюшина, д. 6/10</t>
         </is>
       </c>
     </row>
@@ -678,7 +706,11 @@
           <t>Ремонт</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Михневская, д. 8</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
